--- a/site/exports/cau-science-math.xlsx
+++ b/site/exports/cau-science-math.xlsx
@@ -452,8 +452,8 @@
     <col width="43.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">

--- a/site/exports/cau-science-math.xlsx
+++ b/site/exports/cau-science-math.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="43.4" customWidth="1" min="4" max="4"/>
+    <col width="50.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>应用数学系</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Official university biography supplies partial professional facts only; independent directory and realtime employment unverified.；Degree labels and completed study do not establish degree awards or conferral dates.；Biography reports combined masters/doctoral study; separate masters dates, qualification and award remain unknown; no separate masters award inferred.；No own advisor names retained. Own doctoral-supervisor title does not identify this person’s mentors.；Selected works here are two source-listed software copyright registrations, not academic papers. Rights holders, inventor/developer roles and registry entries not independently verified.；Initial assumed spelling 马晓东 and official URL were checked before first body; corrected official name 马晓栋 was discovered on body and checked afterward with zero matches. Exact-name preflight timing exception is explicitly retained.；No complete publication inventory or full-page/HTTP snapshot is claimed.；来源差异/限制：Education table names 山东大学, biography specifies 山东大学（威海）; retained without inferring an award-granting campus distinction.；来源单位：理学院应用数学系。本站按“应用数学系”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。；来源记载职业信息：职业职称：副教授。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -657,7 +711,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="64.39999999999999" customWidth="1" min="15" max="15"/>
     <col width="58.8" customWidth="1" min="16" max="16"/>
-    <col width="43.4" customWidth="1" min="17" max="17"/>
+    <col width="50.4" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1461,8 +1515,203 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2008-07-01</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>数学与应用数学</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>中科院数学与系统科学研究院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2008-09-01</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>应用数学</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>教师</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学理学院应用数学系</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1474,6 +1723,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1576,7 +1828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1584,11 +1836,11 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="30.8" customWidth="1" min="4" max="4"/>
     <col width="53.2" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="43.4" customWidth="1" min="7" max="7"/>
+    <col width="57.4" customWidth="1" min="6" max="6"/>
+    <col width="50.4" customWidth="1" min="7" max="7"/>
     <col width="43.4" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1771,8 +2023,116 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>基于流模型的自动出价训练系统</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>software_copyright_registration_as_source</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源source_listing_role：listed in personal official profile; excerpt explicitly labels software copyright registration; no holder or contribution role inferred；来源书目信息（registration_number_as_source）：2026SR0915955</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>多约束离线强化学习自动出价训练系统</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>software_copyright_registration_as_source</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源source_listing_role：listed in personal official profile; excerpt explicitly labels software copyright registration; no holder or contribution role inferred；来源书目信息（registration_number_as_source）：2026SR0825088</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1780,6 +2140,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1791,14 +2155,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="39.2" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="64.39999999999999" customWidth="1" min="3" max="3"/>
-    <col width="60.2" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1991,48 +2355,86 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>马晓栋</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-cau-maxiaodong-s001-9f02f9f64cec</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.cau.edu.cn/mxd_7333/</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T05:40:28Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>中国农业大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>王超</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>institution-classification-2</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>https://www.jlu.edu.cn/xxgk.htm</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>历史985院校分类参考；非个人授位或就读当年建设身份的证明</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>未单独记录</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>cau</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>cau</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>中国农业大学</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/cau-science-math.xlsx
+++ b/site/exports/cau-science-math.xlsx
@@ -1556,7 +1556,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
